--- a/templates/site_invoice/template_1.xlsx
+++ b/templates/site_invoice/template_1.xlsx
@@ -12,11 +12,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
   <si>
     <t>Field</t>
   </si>
   <si>
+    <t>TAX INVOICE</t>
+  </si>
+  <si>
     <t>Cell</t>
   </si>
   <si>
@@ -51,9 +54,6 @@
   </si>
   <si>
     <t>Customer PAN</t>
-  </si>
-  <si>
-    <t>TAX INVOICE</t>
   </si>
   <si>
     <t>D9</t>
@@ -236,18 +236,18 @@
     </font>
     <font>
       <b/>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
+      <sz val="8.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -415,7 +415,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="40">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -434,19 +434,19 @@
     </xf>
     <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="9" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="11" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -455,24 +455,21 @@
     <xf borderId="12" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="14" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="14" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="14" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="14" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -484,24 +481,18 @@
     <xf borderId="14" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="15" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="16" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="14" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -509,16 +500,16 @@
     <xf borderId="1" fillId="0" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -753,7 +744,7 @@
   <sheetData>
     <row r="1" ht="24.0" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -838,19 +829,21 @@
       <c r="H8" s="18"/>
     </row>
     <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="20"/>
+      <c r="A9" s="20" t="s">
+        <v>44</v>
+      </c>
       <c r="B9" s="3"/>
       <c r="C9" s="4"/>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="20" t="s">
         <v>44</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="4"/>
-      <c r="G9" s="20"/>
+      <c r="G9" s="21"/>
       <c r="H9" s="4"/>
     </row>
     <row r="10" ht="31.5" customHeight="1">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="20" t="s">
         <v>45</v>
       </c>
       <c r="B10" s="3"/>
@@ -862,32 +855,32 @@
       <c r="H10" s="4"/>
     </row>
     <row r="11" ht="24.75" customHeight="1">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="E11" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="F11" s="23" t="s">
         <v>50</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="4"/>
     </row>
     <row r="12" ht="24.75" customHeight="1">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="25" t="s">
         <v>52</v>
       </c>
       <c r="C12" s="3"/>
@@ -898,123 +891,117 @@
       <c r="H12" s="4"/>
     </row>
     <row r="13" ht="24.75" customHeight="1">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="30"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="29"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="31"/>
+      <c r="H13" s="30"/>
     </row>
     <row r="14" ht="24.75" customHeight="1">
       <c r="A14" s="18"/>
       <c r="B14" s="18"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="30"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="29"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="31"/>
+      <c r="H14" s="30"/>
     </row>
     <row r="15" ht="24.75" customHeight="1">
-      <c r="A15" s="32"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="33"/>
+      <c r="A15" s="31"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="32"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="31"/>
+      <c r="H15" s="30"/>
     </row>
     <row r="16" ht="24.75" customHeight="1">
-      <c r="A16" s="34"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="30"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="29"/>
       <c r="G16" s="3"/>
       <c r="H16" s="4"/>
     </row>
     <row r="17" ht="24.75" customHeight="1">
-      <c r="A17" s="34"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="30"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="29"/>
       <c r="G17" s="3"/>
       <c r="H17" s="4"/>
     </row>
     <row r="18" ht="24.75" customHeight="1">
-      <c r="A18" s="34"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="30"/>
+      <c r="A18" s="33"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="29"/>
       <c r="G18" s="3"/>
       <c r="H18" s="4"/>
     </row>
     <row r="19" ht="24.75" customHeight="1">
-      <c r="A19" s="34"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="30"/>
+      <c r="A19" s="33"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="29"/>
       <c r="G19" s="3"/>
       <c r="H19" s="4"/>
     </row>
     <row r="20" ht="24.75" customHeight="1">
-      <c r="A20" s="35" t="s">
+      <c r="A20" s="29" t="s">
         <v>55</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="4"/>
-      <c r="F20" s="36"/>
+      <c r="F20" s="32"/>
       <c r="G20" s="3"/>
       <c r="H20" s="4"/>
     </row>
     <row r="21" ht="24.75" customHeight="1">
-      <c r="A21" s="37" t="s">
+      <c r="A21" s="34" t="s">
         <v>56</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="4"/>
-      <c r="F21" s="38" t="str">
-        <f>IF(F20=0,"-",F20*0)</f>
-        <v>-</v>
-      </c>
+      <c r="F21" s="35"/>
       <c r="G21" s="3"/>
       <c r="H21" s="4"/>
     </row>
     <row r="22" ht="24.75" customHeight="1">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="34" t="s">
         <v>57</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="4"/>
-      <c r="F22" s="38" t="str">
-        <f>IF(F20=0,"-",F20*0)</f>
-        <v>-</v>
-      </c>
+      <c r="F22" s="35"/>
       <c r="G22" s="3"/>
       <c r="H22" s="4"/>
     </row>
     <row r="23" ht="24.75" customHeight="1">
-      <c r="A23" s="39" t="s">
+      <c r="A23" s="36" t="s">
         <v>58</v>
       </c>
       <c r="B23" s="3"/>
@@ -1025,47 +1012,47 @@
       <c r="G23" s="3"/>
       <c r="H23" s="4"/>
     </row>
-    <row r="24" ht="24.75" customHeight="1">
-      <c r="A24" s="40"/>
+    <row r="24" ht="15.0" customHeight="1">
+      <c r="A24" s="37"/>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
       <c r="D24" s="6"/>
-      <c r="E24" s="41"/>
+      <c r="E24" s="38"/>
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
       <c r="H24" s="6"/>
     </row>
-    <row r="25" ht="24.75" customHeight="1">
+    <row r="25" ht="12.75" customHeight="1">
       <c r="A25" s="8"/>
       <c r="D25" s="9"/>
       <c r="E25" s="8"/>
       <c r="H25" s="9"/>
     </row>
-    <row r="26" ht="24.75" customHeight="1">
+    <row r="26" ht="13.5" customHeight="1">
       <c r="A26" s="8"/>
       <c r="D26" s="9"/>
       <c r="E26" s="8"/>
       <c r="H26" s="9"/>
     </row>
-    <row r="27" ht="24.75" customHeight="1">
+    <row r="27" ht="12.75" customHeight="1">
       <c r="A27" s="8"/>
       <c r="D27" s="9"/>
       <c r="E27" s="8"/>
       <c r="H27" s="9"/>
     </row>
-    <row r="28" ht="24.75" customHeight="1">
+    <row r="28" ht="12.0" customHeight="1">
       <c r="A28" s="8"/>
       <c r="D28" s="9"/>
       <c r="E28" s="8"/>
       <c r="H28" s="9"/>
     </row>
-    <row r="29" ht="24.75" customHeight="1">
+    <row r="29" ht="12.0" customHeight="1">
       <c r="A29" s="8"/>
       <c r="D29" s="9"/>
       <c r="E29" s="8"/>
       <c r="H29" s="9"/>
     </row>
-    <row r="30" ht="24.75" customHeight="1">
+    <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="11"/>
       <c r="B30" s="19"/>
       <c r="C30" s="19"/>
@@ -1073,8 +1060,8 @@
       <c r="E30" s="8"/>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" ht="24.75" customHeight="1">
-      <c r="A31" s="42" t="s">
+    <row r="31" ht="12.0" customHeight="1">
+      <c r="A31" s="39" t="s">
         <v>59</v>
       </c>
       <c r="B31" s="15"/>
@@ -1083,43 +1070,43 @@
       <c r="E31" s="8"/>
       <c r="H31" s="9"/>
     </row>
-    <row r="32" ht="24.75" customHeight="1">
+    <row r="32" ht="12.75" customHeight="1">
       <c r="A32" s="8"/>
       <c r="D32" s="9"/>
       <c r="E32" s="8"/>
       <c r="H32" s="9"/>
     </row>
-    <row r="33" ht="24.75" customHeight="1">
+    <row r="33" ht="8.25" customHeight="1">
       <c r="A33" s="8"/>
       <c r="D33" s="9"/>
       <c r="E33" s="8"/>
       <c r="H33" s="9"/>
     </row>
-    <row r="34" ht="24.75" customHeight="1">
+    <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="8"/>
       <c r="D34" s="9"/>
       <c r="E34" s="8"/>
       <c r="H34" s="9"/>
     </row>
-    <row r="35" ht="24.75" customHeight="1">
+    <row r="35" ht="12.75" customHeight="1">
       <c r="A35" s="8"/>
       <c r="D35" s="9"/>
       <c r="E35" s="8"/>
       <c r="H35" s="9"/>
     </row>
-    <row r="36" ht="24.75" customHeight="1">
+    <row r="36" ht="12.0" customHeight="1">
       <c r="A36" s="8"/>
       <c r="D36" s="9"/>
       <c r="E36" s="8"/>
       <c r="H36" s="9"/>
     </row>
-    <row r="37" ht="24.75" customHeight="1">
+    <row r="37" ht="9.0" customHeight="1">
       <c r="A37" s="8"/>
       <c r="D37" s="9"/>
       <c r="E37" s="8"/>
       <c r="H37" s="9"/>
     </row>
-    <row r="38" ht="24.75" customHeight="1">
+    <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="11"/>
       <c r="B38" s="19"/>
       <c r="C38" s="19"/>
@@ -2093,21 +2080,6 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="F19:H19"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="H5:H6"/>
     <mergeCell ref="G7:G8"/>
@@ -2119,16 +2091,31 @@
     <mergeCell ref="C4:H4"/>
     <mergeCell ref="A5:C8"/>
     <mergeCell ref="D5:F8"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A21:E21"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A24:D30"/>
-    <mergeCell ref="E24:H38"/>
     <mergeCell ref="A31:D38"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="F11:H11"/>
     <mergeCell ref="F13:H13"/>
-    <mergeCell ref="F14:H14"/>
     <mergeCell ref="F15:H15"/>
     <mergeCell ref="F16:H16"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="F18:H18"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="E24:H38"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.25" footer="0.0" header="0.0" left="0.25" right="0.25" top="0.25"/>
@@ -2158,48 +2145,48 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>14</v>

--- a/templates/site_invoice/template_1.xlsx
+++ b/templates/site_invoice/template_1.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
   <si>
     <t>Field</t>
   </si>
@@ -194,7 +194,10 @@
     <t>Add : SGST @ 9 % Of Gross</t>
   </si>
   <si>
-    <t xml:space="preserve">Total Amt In Word :- </t>
+    <t>Total Amt In Word :-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand Total.  </t>
   </si>
   <si>
     <t>‘I/We hereby certify that my/our registration certificate under the Maharashtra Value Added Tax Act. 2002 is in force on the date on which the sale of the goods specified in this tax invoice is made by me/us and that the transaction of sale covered by this tax invoice has been effected by me/us and it shall be accounted for in the turDECer of sale while filling of return and the due if any payable on the sale has been paid’.</t>
@@ -204,7 +207,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -247,6 +250,12 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <sz val="9.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="8.0"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -266,7 +275,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="20">
     <border/>
     <border>
       <left style="thin">
@@ -411,11 +420,47 @@
         <color rgb="FF808080"/>
       </bottom>
     </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -500,8 +545,15 @@
     <xf borderId="1" fillId="0" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="17" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="18" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="19" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -509,7 +561,7 @@
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1007,17 +1059,19 @@
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="G23" s="39"/>
       <c r="H23" s="4"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="37"/>
+      <c r="A24" s="40"/>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
       <c r="D24" s="6"/>
-      <c r="E24" s="38"/>
+      <c r="E24" s="41"/>
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
       <c r="H24" s="6"/>
@@ -1061,8 +1115,8 @@
       <c r="H30" s="9"/>
     </row>
     <row r="31" ht="12.0" customHeight="1">
-      <c r="A31" s="39" t="s">
-        <v>59</v>
+      <c r="A31" s="42" t="s">
+        <v>60</v>
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -2079,7 +2133,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="37">
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="H5:H6"/>
     <mergeCell ref="G7:G8"/>
@@ -2095,6 +2149,7 @@
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:D30"/>
     <mergeCell ref="A31:D38"/>
     <mergeCell ref="A9:C9"/>
@@ -2107,7 +2162,8 @@
     <mergeCell ref="F20:H20"/>
     <mergeCell ref="F21:H21"/>
     <mergeCell ref="F22:H22"/>
-    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="E24:H38"/>
     <mergeCell ref="F11:H11"/>
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="F15:H15"/>
@@ -2115,7 +2171,6 @@
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="F18:H18"/>
     <mergeCell ref="F19:H19"/>
-    <mergeCell ref="E24:H38"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.25" footer="0.0" header="0.0" left="0.25" right="0.25" top="0.25"/>

--- a/templates/site_invoice/template_1.xlsx
+++ b/templates/site_invoice/template_1.xlsx
@@ -125,17 +125,17 @@
     <t>CGST</t>
   </si>
   <si>
-    <t>F21</t>
-  </si>
-  <si>
-    <t>SGST</t>
-  </si>
-  <si>
-    <t>F22</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bill From,
 </t>
+  </si>
+  <si>
+    <t>F21</t>
+  </si>
+  <si>
+    <t>SGST</t>
+  </si>
+  <si>
+    <t>F22</t>
   </si>
   <si>
     <t xml:space="preserve">Bill To,
@@ -207,6 +207,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
   <fonts count="10">
     <font>
       <sz val="11.0"/>
@@ -217,7 +221,6 @@
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -460,7 +463,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="41">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -475,7 +478,7 @@
     </xf>
     <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -488,7 +491,7 @@
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="11" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -499,9 +502,6 @@
     </xf>
     <xf borderId="12" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -520,9 +520,6 @@
     <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="14" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -539,30 +536,30 @@
     <xf borderId="14" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="17" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="18" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="19" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="19" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -791,7 +788,6 @@
     <col customWidth="1" min="4" max="4" width="14.0"/>
     <col customWidth="1" min="5" max="6" width="18.0"/>
     <col customWidth="1" min="7" max="8" width="14.0"/>
-    <col customWidth="1" min="9" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="24.0" customHeight="1">
@@ -838,7 +834,7 @@
     </row>
     <row r="5" ht="19.5" customHeight="1">
       <c r="A5" s="14" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="6"/>
@@ -891,7 +887,7 @@
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="4"/>
-      <c r="G9" s="21"/>
+      <c r="G9" s="20"/>
       <c r="H9" s="4"/>
     </row>
     <row r="10" ht="31.5" customHeight="1">
@@ -907,32 +903,32 @@
       <c r="H10" s="4"/>
     </row>
     <row r="11" ht="24.75" customHeight="1">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="23" t="s">
+      <c r="F11" s="22" t="s">
         <v>50</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="4"/>
     </row>
     <row r="12" ht="24.75" customHeight="1">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="24" t="s">
         <v>52</v>
       </c>
       <c r="C12" s="3"/>
@@ -943,81 +939,81 @@
       <c r="H12" s="4"/>
     </row>
     <row r="13" ht="24.75" customHeight="1">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="29"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="27"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="30"/>
+      <c r="H13" s="28"/>
     </row>
     <row r="14" ht="24.75" customHeight="1">
       <c r="A14" s="18"/>
       <c r="B14" s="18"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="29"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="27"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="30"/>
+      <c r="H14" s="28"/>
     </row>
     <row r="15" ht="24.75" customHeight="1">
-      <c r="A15" s="31"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="32"/>
+      <c r="A15" s="29"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="30"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="30"/>
+      <c r="H15" s="28"/>
     </row>
     <row r="16" ht="24.75" customHeight="1">
-      <c r="A16" s="33"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="29"/>
+      <c r="A16" s="31"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="27"/>
       <c r="G16" s="3"/>
       <c r="H16" s="4"/>
     </row>
     <row r="17" ht="24.75" customHeight="1">
-      <c r="A17" s="33"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="29"/>
+      <c r="A17" s="31"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="27"/>
       <c r="G17" s="3"/>
       <c r="H17" s="4"/>
     </row>
     <row r="18" ht="24.75" customHeight="1">
-      <c r="A18" s="33"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="29"/>
+      <c r="A18" s="31"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="27"/>
       <c r="G18" s="3"/>
       <c r="H18" s="4"/>
     </row>
     <row r="19" ht="24.75" customHeight="1">
-      <c r="A19" s="33"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="29"/>
+      <c r="A19" s="31"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="27"/>
       <c r="G19" s="3"/>
       <c r="H19" s="4"/>
     </row>
     <row r="20" ht="24.75" customHeight="1">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="27" t="s">
         <v>55</v>
       </c>
       <c r="B20" s="3"/>
@@ -1029,49 +1025,49 @@
       <c r="H20" s="4"/>
     </row>
     <row r="21" ht="24.75" customHeight="1">
-      <c r="A21" s="34" t="s">
+      <c r="A21" s="33" t="s">
         <v>56</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="4"/>
-      <c r="F21" s="35"/>
+      <c r="F21" s="34"/>
       <c r="G21" s="3"/>
       <c r="H21" s="4"/>
     </row>
     <row r="22" ht="24.75" customHeight="1">
-      <c r="A22" s="34" t="s">
+      <c r="A22" s="33" t="s">
         <v>57</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="4"/>
-      <c r="F22" s="35"/>
+      <c r="F22" s="34"/>
       <c r="G22" s="3"/>
       <c r="H22" s="4"/>
     </row>
     <row r="23" ht="24.75" customHeight="1">
-      <c r="A23" s="36" t="s">
+      <c r="A23" s="35" t="s">
         <v>58</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="38" t="s">
+      <c r="E23" s="36"/>
+      <c r="F23" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="G23" s="39"/>
+      <c r="G23" s="38"/>
       <c r="H23" s="4"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="40"/>
+      <c r="A24" s="39"/>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
       <c r="D24" s="6"/>
-      <c r="E24" s="41"/>
+      <c r="E24" s="5"/>
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
       <c r="H24" s="6"/>
@@ -1115,7 +1111,7 @@
       <c r="H30" s="9"/>
     </row>
     <row r="31" ht="12.0" customHeight="1">
-      <c r="A31" s="42" t="s">
+      <c r="A31" s="40" t="s">
         <v>60</v>
       </c>
       <c r="B31" s="15"/>
@@ -2192,7 +2188,7 @@
     <col customWidth="1" min="1" max="1" width="25.0"/>
     <col customWidth="1" min="2" max="2" width="14.0"/>
     <col customWidth="1" min="3" max="3" width="55.0"/>
-    <col customWidth="1" min="4" max="26" width="8.71"/>
+    <col customWidth="1" min="4" max="6" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2332,7 +2328,7 @@
         <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>35</v>
@@ -2340,10 +2336,10 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>35</v>

--- a/templates/site_invoice/template_1.xlsx
+++ b/templates/site_invoice/template_1.xlsx
@@ -125,17 +125,17 @@
     <t>CGST</t>
   </si>
   <si>
+    <t>F21</t>
+  </si>
+  <si>
+    <t>SGST</t>
+  </si>
+  <si>
+    <t>F22</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bill From,
 </t>
-  </si>
-  <si>
-    <t>F21</t>
-  </si>
-  <si>
-    <t>SGST</t>
-  </si>
-  <si>
-    <t>F22</t>
   </si>
   <si>
     <t xml:space="preserve">Bill To,
@@ -207,9 +207,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -552,7 +551,7 @@
     <xf borderId="18" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="19" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="19" fillId="0" fontId="8" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -834,7 +833,7 @@
     </row>
     <row r="5" ht="19.5" customHeight="1">
       <c r="A5" s="14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="6"/>
@@ -2328,7 +2327,7 @@
         <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>35</v>
@@ -2336,10 +2335,10 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>35</v>
